--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Scuola primaria e secondaria (1).xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Scuola primaria e secondaria (1).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="160">
   <si>
     <r>
       <t xml:space="preserve">
@@ -1414,8 +1414,8 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Se hai già provveduto a pagare l'avviso ignora questo messaggio.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
@@ -2190,10 +2190,13 @@
     <t>Vai alla graduatoria</t>
   </si>
   <si>
-    <t>Vedi Avviso</t>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <t>Vedi ricevuta</t>
+  </si>
+  <si>
+    <t>Vedi Avviso</t>
   </si>
   <si>
     <r>
@@ -3257,7 +3260,7 @@
         <v>124</v>
       </c>
       <c r="Q6" s="34" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R6" s="34" t="s">
         <v>121</v>
@@ -3268,7 +3271,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>68</v>
@@ -3327,7 +3330,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>121</v>
@@ -3386,125 +3389,125 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G9" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="M9" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="N9" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="O9" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="P9" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q9" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="H9" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="J9" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="K9" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="L9" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="M9" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="N9" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="O9" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="P9" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q9" s="34" t="s">
-        <v>129</v>
-      </c>
       <c r="R9" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="S9" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J10" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L10" s="34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M10" s="34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O10" s="34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P10" s="34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q10" s="34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="R10" s="34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S10" s="34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>68</v>
@@ -3525,13 +3528,13 @@
         <v>68</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J11" s="34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K11" s="34" t="s">
         <v>68</v>
